--- a/excel/distribuidora-cunza-s-a_capacitaciones.xlsx
+++ b/excel/distribuidora-cunza-s-a_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C004095705</t>
+          <t>C000543457</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C004095705 - CAMA CAPIA ROSALINA</t>
+          <t>C000543457 - MONTIALI ARIAS NANCY REINA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -629,11 +629,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -648,7 +644,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -682,7 +678,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -692,12 +688,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C004098991</t>
+          <t>C000544151</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C004098991 - RUIZ VALDERRAMA LUZMILA</t>
+          <t>C000544151 - FERNANDEZ MENDOZA ROSARIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -760,7 +756,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -770,17 +766,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C004099026</t>
+          <t>C001719408</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C004099026 - BORRAJERO RODRIGO KATHERYN KELLY</t>
+          <t>C001719408 - BUSTAMANTE DELGADO MARIALUISA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -793,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -804,9 +800,21 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
@@ -848,12 +856,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C004175227</t>
+          <t>C001757302</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C004175227 - SUNI SANTOYO MARISOL</t>
+          <t>C001757302 - CORNEJO ESPIRITU ROSA SUSANA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -889,7 +897,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -938,12 +946,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C004054830</t>
+          <t>C001750233</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C004054830 - RIOS VELA DEIDITH</t>
+          <t>C001750233 - HUAMANI GOMEZ ROBERTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -979,7 +987,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1028,12 +1036,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C004177436</t>
+          <t>C004022016</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C004177436 - LLOCCLLA JANAMPA FERMIN</t>
+          <t>C004022016 - GARAMENDI PRADO DE BERROCAL OLINDA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1064,12 +1072,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1118,12 +1126,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C004022016</t>
+          <t>C004022179</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C004022016 - GARAMENDI PRADO DE BERROCAL OLINDA</t>
+          <t>C004022179 - MENDOZA ANDRADE ALVARO JOSE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1154,7 +1162,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1208,12 +1216,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C004022179</t>
+          <t>C004025463</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C004022179 - MENDOZA ANDRADE ALVARO JOSE</t>
+          <t>C004025463 - TRIBIÑOS MUÑOZ LULY</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1249,7 +1257,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1298,12 +1306,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C004025463</t>
+          <t>C004095705</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C004025463 - TRIBIÑOS MUÑOZ LULY</t>
+          <t>C004095705 - CAMA CAPIA ROSALINA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1329,17 +1337,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1388,12 +1400,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001750233</t>
+          <t>C004054830</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C001750233 - HUAMANI GOMEZ ROBERTA</t>
+          <t>C004054830 - RIOS VELA DEIDITH</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1429,7 +1441,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1478,12 +1490,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001757302</t>
+          <t>C004177436</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001757302 - CORNEJO ESPIRITU ROSA SUSANA</t>
+          <t>C004177436 - LLOCCLLA JANAMPA FERMIN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1519,7 +1531,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1568,12 +1580,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001719408</t>
+          <t>C004175227</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001719408 - BUSTAMANTE DELGADO MARIALUISA</t>
+          <t>C004175227 - SUNI SANTOYO MARISOL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1604,7 +1616,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1648,7 +1660,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1658,17 +1670,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001696599</t>
+          <t>C004098991</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001696599 - MANCILLA ZAVALETA DE SANCHO SANTOS GLORI</t>
+          <t>C004098991 - RUIZ VALDERRAMA LUZMILA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1681,7 +1693,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1692,21 +1704,9 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1748,17 +1748,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001672567</t>
+          <t>C004099026</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001672567 - SANTANA BARRETO HORLANDINA</t>
+          <t>C004099026 - BORRAJERO RODRIGO KATHERYN KELLY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1782,21 +1782,9 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
@@ -1838,12 +1826,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001662896</t>
+          <t>C004221247</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C001662896 - JIMENEZ CASTILLA NAARA LORENA</t>
+          <t>C004221247 - MUÑOZ CHALA HILDA MELIZA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1874,12 +1862,12 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1928,12 +1916,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001578646</t>
+          <t>C004239620</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001578646 - CARBAJAL AREVALO GILBERTA</t>
+          <t>C004239620 - CCASA CHECA OSWALDO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1969,7 +1957,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2018,12 +2006,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001414451</t>
+          <t>C004236926</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C001414451 - VALENCIA CHUQUIJA ANSELMA</t>
+          <t>C004236926 - AQUINO AQUINO JORGE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2059,7 +2047,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2108,12 +2096,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C000543457</t>
+          <t>C001578646</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C000543457 - MONTIALI ARIAS NANCY REINA</t>
+          <t>C001578646 - CARBAJAL AREVALO GILBERTA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2144,7 +2132,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2154,7 +2142,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2188,7 +2176,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2198,17 +2186,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C000544151</t>
+          <t>C001672567</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C000544151 - FERNANDEZ MENDOZA ROSARIO</t>
+          <t>C001672567 - SANTANA BARRETO HORLANDINA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -2221,7 +2209,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2232,9 +2220,21 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001016514</t>
+          <t>C001662896</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001016514 - VELIZ RAMOS LIDIA</t>
+          <t>C001662896 - JIMENEZ CASTILLA NAARA LORENA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2312,12 +2312,12 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C004239620</t>
+          <t>C001696599</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C004239620 - CCASA CHECA OSWALDO</t>
+          <t>C001696599 - MANCILLA ZAVALETA DE SANCHO SANTOS GLORI</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2456,12 +2456,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004236926</t>
+          <t>C001414451</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C004236926 - AQUINO AQUINO JORGE</t>
+          <t>C001414451 - VALENCIA CHUQUIJA ANSELMA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004221247</t>
+          <t>C001016514</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C004221247 - MUÑOZ CHALA HILDA MELIZA</t>
+          <t>C001016514 - VELIZ RAMOS LIDIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001472910</t>
+          <t>C004214301</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001472910 - COMERCIAL N &amp; M - NIKO Y MECHE S.A.C.</t>
+          <t>C004214301 - HUAQUISACA LIMACHI EUGENIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2852,17 +2852,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001531838</t>
+          <t>C004166585</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001531838 - PISFIL TORRES MARIA ELENA</t>
+          <t>C004166585 - RESURRECCION YANAVILCA DANIELA ARIANA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001562971</t>
+          <t>C004181050</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001562971 - ZAVALETA VIDARTE MARIA ELENA</t>
+          <t>C004181050 - VALDERA ESPINOZA JULIA ARLITA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001646320</t>
+          <t>C004187454</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001646320 - CHUQUIJA PACCO DOMINGO</t>
+          <t>C004187454 - FLORES ANDIA MILAGROS SAYURI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3122,7 +3122,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C004181050</t>
+          <t>C004048053</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C004181050 - VALDERA ESPINOZA JULIA ARLITA</t>
+          <t>C004048053 - QUISPE VILLALVA MARTHA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3212,17 +3212,17 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C004166585</t>
+          <t>C001743773</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C004166585 - RESURRECCION YANAVILCA DANIELA ARIANA</t>
+          <t>C001743773 - HUAMAN ARCEGA ALICIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3302,17 +3302,17 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C004048053</t>
+          <t>C004032353</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C004048053 - QUISPE VILLALVA MARTHA</t>
+          <t>C004032353 - FERNANDEZ ILATOMA MARIBEL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3392,7 +3392,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004214301</t>
+          <t>C001757782</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C004214301 - HUAQUISACA LIMACHI EUGENIA</t>
+          <t>C001757782 - ESPINOZA HUAMAN LUCILA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3482,7 +3482,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C004187454</t>
+          <t>C001747542</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C004187454 - FLORES ANDIA MILAGROS SAYURI</t>
+          <t>C001747542 - SUAVO FLORES RICARDO HIGINIO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001757782</t>
+          <t>C001738646</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001757782 - ESPINOZA HUAMAN LUCILA</t>
+          <t>C001738646 - CUZCANO CARBONERO MAXIMINA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001743773</t>
+          <t>C001736651</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001743773 - HUAMAN ARCEGA ALICIA</t>
+          <t>C001736651 - QUIROZ CORNEJO LAURA MARGARITA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004032353</t>
+          <t>C001738624</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C004032353 - FERNANDEZ ILATOMA MARIBEL</t>
+          <t>C001738624 - PACORA PALACIOS FLOR DE MARIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3842,17 +3842,17 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001747542</t>
+          <t>C001714577</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001747542 - SUAVO FLORES RICARDO HIGINIO</t>
+          <t>C001714577 - GUERRA POVEDA PETRONILA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001738624</t>
+          <t>C001682768</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001738624 - PACORA PALACIOS FLOR DE MARIA</t>
+          <t>C001682768 - ÑAHUIS MENDOZA MAXIMO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4022,17 +4022,17 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001738646</t>
+          <t>C001729220</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C001738646 - CUZCANO CARBONERO MAXIMINA</t>
+          <t>C001729220 - MORALES OSCO RICHARD GUMERCINDO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4112,12 +4112,12 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001736651</t>
+          <t>C001531838</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C001736651 - QUIROZ CORNEJO LAURA MARGARITA</t>
+          <t>C001531838 - PISFIL TORRES MARIA ELENA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4202,12 +4202,12 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001729220</t>
+          <t>C001562971</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001729220 - MORALES OSCO RICHARD GUMERCINDO</t>
+          <t>C001562971 - ZAVALETA VIDARTE MARIA ELENA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4292,7 +4292,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4346,12 +4346,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001682768</t>
+          <t>C001472910</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001682768 - ÑAHUIS MENDOZA MAXIMO</t>
+          <t>C001472910 - COMERCIAL N &amp; M - NIKO Y MECHE S.A.C.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001714577</t>
+          <t>C001646320</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001714577 - GUERRA POVEDA PETRONILA</t>
+          <t>C001646320 - CHUQUIJA PACCO DOMINGO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4472,7 +4472,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001525506</t>
+          <t>C001741233</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001525506 - ALLCCA TINTAYA AMBROCIA</t>
+          <t>C001741233 - SUPO ROMAN DE MENDOZA JULIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001623779</t>
+          <t>C001635189</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001623779 - HUARHUACHI HUACRE MARIA LUZ</t>
+          <t>C001635189 - SIFUENTES ESTRADA DOMITILA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4742,7 +4742,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C000511786</t>
+          <t>C001623779</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C000511786 - NARAZA PRADO NATALIA</t>
+          <t>C001623779 - HUARHUACHI HUACRE MARIA LUZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4832,12 +4832,12 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C000427085</t>
+          <t>C004255932</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C000427085 - ROMERO ALEJANDRO NEDA</t>
+          <t>C004255932 - ESPIRITU RAMIREZ KIMBERLY NICOLE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5156,17 +5156,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001703308</t>
+          <t>C000511786</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001703308 - VILA VILA EMILY SINDY</t>
+          <t>C000511786 - NARAZA PRADO NATALIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5190,9 +5190,21 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
@@ -5224,7 +5236,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5234,17 +5246,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C004239275</t>
+          <t>C001703308</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C004239275 - CIRIACO RODRIGUEZ RUBEN BICET</t>
+          <t>C001703308 - VILA VILA EMILY SINDY</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -5257,7 +5269,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5268,21 +5280,9 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
@@ -5324,12 +5324,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C004255932</t>
+          <t>C001710988</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C004255932 - ESPIRITU RAMIREZ KIMBERLY NICOLE</t>
+          <t>C001710988 - VERDI CRUZ NELY NORMA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5360,12 +5360,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C004180800</t>
+          <t>C004029938</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C004180800 - CONDORI UNUCUECA MIRTHA CAROLINA</t>
+          <t>C004029938 - BETO TEC STORE E.I.R.L.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5450,7 +5450,7 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001398120</t>
+          <t>C001749942</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C001398120 - NOSTADES QUISPE KAREN JANNET</t>
+          <t>C001749942 - AQUISE HUACANI FLOR TRINIDAD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5540,7 +5540,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C000544553</t>
+          <t>C001757080</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C000544553 - CHIRINOS MORIANO ALICIA</t>
+          <t>C001757080 - ROMERO SAMANEZ DE QUISPE ROSA AMABILIA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5630,17 +5630,17 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001635189</t>
+          <t>C001717374</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C001635189 - SIFUENTES ESTRADA DOMITILA</t>
+          <t>C001717374 - PAREDES PAREDES DE HANCCO RAIMONDA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C004190558</t>
+          <t>C004180800</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C004190558 - PADILLA AMIA CRISTINA ELISA</t>
+          <t>C004180800 - CONDORI UNUCUECA MIRTHA CAROLINA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004207454</t>
+          <t>C004183653</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C004207454 - TUMBA GOMEZ LUCY CARMEN</t>
+          <t>C004183653 - TORRES ROMANI LUZ ESTHER</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5990,7 +5990,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001757080</t>
+          <t>C004207454</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C001757080 - ROMERO SAMANEZ DE QUISPE ROSA AMABILIA</t>
+          <t>C004207454 - TUMBA GOMEZ LUCY CARMEN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S63" t="inlineStr"/>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001741233</t>
+          <t>C004190558</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001741233 - SUPO ROMAN DE MENDOZA JULIA</t>
+          <t>C004190558 - PADILLA AMIA CRISTINA ELISA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001749942</t>
+          <t>C004239275</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001749942 - AQUISE HUACANI FLOR TRINIDAD</t>
+          <t>C004239275 - CIRIACO RODRIGUEZ RUBEN BICET</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6265,12 +6265,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001710988</t>
+          <t>C000427085</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001710988 - VERDI CRUZ NELY NORMA</t>
+          <t>C000427085 - ROMERO ALEJANDRO NEDA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6350,12 +6350,12 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001474012</t>
+          <t>C000544553</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C001474012 - RAMOS HUAYTA SOFIA ESPERANZA</t>
+          <t>C000544553 - CHIRINOS MORIANO ALICIA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S67" t="inlineStr"/>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001717374</t>
+          <t>C001525506</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C001717374 - PAREDES PAREDES DE HANCCO RAIMONDA</t>
+          <t>C001525506 - ALLCCA TINTAYA AMBROCIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C004029938</t>
+          <t>C001474012</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C004029938 - BETO TEC STORE E.I.R.L.</t>
+          <t>C001474012 - RAMOS HUAYTA SOFIA ESPERANZA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C004183653</t>
+          <t>C001398120</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C004183653 - TORRES ROMANI LUZ ESTHER</t>
+          <t>C001398120 - NOSTADES QUISPE KAREN JANNET</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C004016494</t>
+          <t>C001755476</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C004016494 - VALENCIA GAMARRA MARCELINO</t>
+          <t>C001755476 - HUAMAN PEÑALOZA HILDA YSABEL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6800,17 +6800,17 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S71" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6854,17 +6854,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001737021</t>
+          <t>C001755579</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001737021 - VALLEJOS JINEZ GUILIANA ELVIRA</t>
+          <t>C001755579 - YUPA MALLQUI FLOR ANGELA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6888,9 +6888,21 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr">
         <is>
@@ -6932,12 +6944,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001736451</t>
+          <t>C004094278</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001736451 - CAILLAHUA FUENTES MARCELINA VALERIANA</t>
+          <t>C004094278 - QUISPE BAEZ ELSA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7022,12 +7034,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001515304</t>
+          <t>C004098638</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001515304 - ROQUE DIAZ TANIA ERIKA</t>
+          <t>C004098638 - MENDOZA GOMEZ HERLINDA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7058,7 +7070,7 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -7102,7 +7114,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7112,17 +7124,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001535816</t>
+          <t>C004176145</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001535816 - RAYMUNDO BERNAL HECTOR</t>
+          <t>C004176145 - ARANDA PARDO ANDERSON GILBERT</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
@@ -7135,7 +7147,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7146,21 +7158,9 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
@@ -7202,12 +7202,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C000426819</t>
+          <t>C004181018</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C000426819 - AGUIRRE QUINTANA CARMEN</t>
+          <t>C004181018 - BLANCO QUISPE YOVANNA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7238,12 +7238,12 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C000427409</t>
+          <t>C004170770</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C000427409 - OCHOA MARTINEZ SANTIAGO</t>
+          <t>C004170770 - GOMEZ TINTAYA JOSE WILFREDO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7328,12 +7328,12 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C000511587</t>
+          <t>C004200844</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C000511587 - HUARANCCA LENES ANA</t>
+          <t>C004200844 - CUYA HUACHUHUILLCA FORTUNATA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7418,12 +7418,12 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C004170770</t>
+          <t>C004207921</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C004170770 - GOMEZ TINTAYA JOSE WILFREDO</t>
+          <t>C004207921 - ESTRELLA ALDERETE MAGALI SONIA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C004094278</t>
+          <t>C001535816</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C004094278 - QUISPE BAEZ ELSA</t>
+          <t>C001535816 - RAYMUNDO BERNAL HECTOR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7598,17 +7598,17 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
@@ -7652,12 +7652,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C001755579</t>
+          <t>C000426819</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C001755579 - YUPA MALLQUI FLOR ANGELA</t>
+          <t>C000426819 - AGUIRRE QUINTANA CARMEN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7688,12 +7688,12 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C004165557</t>
+          <t>C000427409</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C004165557 - VELASQUEZ MERCADO EVELYN</t>
+          <t>C000427409 - OCHOA MARTINEZ SANTIAGO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7832,12 +7832,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C004201522</t>
+          <t>C000511587</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C004201522 - RICARDO CHAVEZ E.I.R.L.</t>
+          <t>C000511587 - HUARANCCA LENES ANA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7868,12 +7868,12 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7922,12 +7922,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C004167725</t>
+          <t>C004201522</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C004167725 - MENDOZA TELLO ROBERTA JULIA</t>
+          <t>C004201522 - RICARDO CHAVEZ E.I.R.L.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7958,17 +7958,17 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C001757996</t>
+          <t>C004045205</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>C001757996 - INGARUCA RIVAS LESLIE MILAGROS</t>
+          <t>C004045205 - BENDITA QUISPE NATI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8048,12 +8048,12 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C001755476</t>
+          <t>C004167725</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C001755476 - HUAMAN PEÑALOZA HILDA YSABEL</t>
+          <t>C004167725 - MENDOZA TELLO ROBERTA JULIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8138,17 +8138,17 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S86" t="inlineStr"/>
@@ -8192,12 +8192,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C004045205</t>
+          <t>C004165557</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>C004045205 - BENDITA QUISPE NATI</t>
+          <t>C004165557 - VELASQUEZ MERCADO EVELYN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -8228,7 +8228,7 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C004098638</t>
+          <t>C001757996</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C004098638 - MENDOZA GOMEZ HERLINDA</t>
+          <t>C001757996 - INGARUCA RIVAS LESLIE MILAGROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8318,12 +8318,12 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8372,17 +8372,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C004207921</t>
+          <t>C001737021</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C004207921 - ESTRELLA ALDERETE MAGALI SONIA</t>
+          <t>C001737021 - VALLEJOS JINEZ GUILIANA ELVIRA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -8406,21 +8406,9 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr">
         <is>
@@ -8462,12 +8450,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004200844</t>
+          <t>C001736451</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C004200844 - CUYA HUACHUHUILLCA FORTUNATA</t>
+          <t>C001736451 - CAILLAHUA FUENTES MARCELINA VALERIANA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8552,12 +8540,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C004181018</t>
+          <t>C004016494</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C004181018 - BLANCO QUISPE YOVANNA</t>
+          <t>C004016494 - VALENCIA GAMARRA MARCELINO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8598,7 +8586,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S91" t="inlineStr"/>
@@ -8632,7 +8620,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8642,17 +8630,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C004176145</t>
+          <t>C001515304</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C004176145 - ARANDA PARDO ANDERSON GILBERT</t>
+          <t>C001515304 - ROQUE DIAZ TANIA ERIKA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -8665,7 +8653,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -8676,9 +8664,21 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr">
         <is>
@@ -11940,12 +11940,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C004184529</t>
+          <t>C004166622</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C004184529 - LUIS RAMOS DE ZAVALETA ZENOVIA CLAUDIA</t>
+          <t>C004166622 - LOZADA PILLCO JOHN CARLO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11976,17 +11976,17 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S129" t="inlineStr"/>
@@ -12120,12 +12120,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C004166622</t>
+          <t>C004184529</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C004166622 - LOZADA PILLCO JOHN CARLO</t>
+          <t>C004184529 - LUIS RAMOS DE ZAVALETA ZENOVIA CLAUDIA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12156,17 +12156,17 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S131" t="inlineStr"/>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12836,17 +12836,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C001679814</t>
+          <t>C004023132</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>C001679814 - ANDRADE YABARINO ALEXANDRA FABIOLA</t>
+          <t>C004023132 - TOCTO LLACSAHUANGA DELIXABEL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -12870,21 +12870,9 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>Agregar productos al carrito</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr">
         <is>
@@ -13200,12 +13188,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C000423530</t>
+          <t>C001679814</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>C000423530 - CAVERO BENITES SERGIO</t>
+          <t>C001679814 - ANDRADE YABARINO ALEXANDRA FABIOLA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13236,17 +13224,17 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S143" t="inlineStr"/>
@@ -13280,7 +13268,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13290,17 +13278,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C000423757</t>
+          <t>C000423530</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>C000423757 - ARMACANQUI FLORES ETELVINA</t>
+          <t>C000423530 - CAVERO BENITES SERGIO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
@@ -13313,7 +13301,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -13324,9 +13312,21 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13368,17 +13368,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C000424427</t>
+          <t>C000423757</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>C000424427 - PAMPAMALLCO APAZA DE TOLEDO LEONOR</t>
+          <t>C000423757 - ARMACANQUI FLORES ETELVINA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -13402,21 +13402,9 @@
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
       <c r="T145" t="inlineStr">
         <is>
@@ -13458,12 +13446,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C004099868</t>
+          <t>C000424427</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>C004099868 - ECO STAR S.A.C.</t>
+          <t>C000424427 - PAMPAMALLCO APAZA DE TOLEDO LEONOR</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13499,12 +13487,12 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S146" t="inlineStr"/>
@@ -13538,7 +13526,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13548,17 +13536,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C004023132</t>
+          <t>C004099868</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>C004023132 - TOCTO LLACSAHUANGA DELIXABEL</t>
+          <t>C004099868 - ECO STAR S.A.C.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
@@ -13571,7 +13559,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -13582,9 +13570,21 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr">
         <is>
@@ -13626,12 +13626,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>C004171595</t>
+          <t>C004164170</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>C004171595 - DONDE SIEMPRE S.A.C.</t>
+          <t>C004164170 - ESPINO SARAVIA MARTIN ELEODORO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S148" t="inlineStr"/>
@@ -13716,12 +13716,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C004164170</t>
+          <t>C004171595</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C004164170 - ESPINO SARAVIA MARTIN ELEODORO</t>
+          <t>C004171595 - DONDE SIEMPRE S.A.C.</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
@@ -14076,12 +14076,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C004099736</t>
+          <t>C004186892</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C004099736 - WILHELM BELTRAN HELMUT ERNESTO</t>
+          <t>C004186892 - HUAMANI FLORES DAVID GILMER</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14112,12 +14112,12 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
@@ -14166,12 +14166,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C004186892</t>
+          <t>C004099736</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C004186892 - HUAMANI FLORES DAVID GILMER</t>
+          <t>C004099736 - WILHELM BELTRAN HELMUT ERNESTO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14202,12 +14202,12 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C004165976</t>
+          <t>C004183386</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C004165976 - QUIROZ HUANGAL MIREILI NORELI</t>
+          <t>C004183386 - HUAYAS TICSE NANCY PILAR</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S155" t="inlineStr"/>
@@ -14346,12 +14346,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C004183386</t>
+          <t>C004167204</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>C004183386 - HUAYAS TICSE NANCY PILAR</t>
+          <t>C004167204 - OJEDA YARANGA NERIO SILVIO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14382,17 +14382,17 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S156" t="inlineStr"/>
@@ -14436,12 +14436,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C004167204</t>
+          <t>C004165976</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>C004167204 - OJEDA YARANGA NERIO SILVIO</t>
+          <t>C004165976 - QUIROZ HUANGAL MIREILI NORELI</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -14472,12 +14472,12 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -15070,12 +15070,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>C001744771</t>
+          <t>C004236752</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>C001744771 - CORTES PEREZ CARLOS ALBERTO</t>
+          <t>C004236752 - AURORA QUISPE MARLENE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15106,7 +15106,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -15116,19 +15116,23 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U164" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -15160,12 +15164,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>C001757487</t>
+          <t>C004047434</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>C001757487 - MERCADO VELIZ JUAN CARLOS</t>
+          <t>C004047434 - PACHECO GUILLEN ABDON JESUS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15196,12 +15200,12 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -15250,12 +15254,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001703694</t>
+          <t>C001757487</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C001703694 - OSPINA VARGAS LILIANA MARIBEL</t>
+          <t>C001757487 - MERCADO VELIZ JUAN CARLOS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -15281,11 +15285,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S166" t="inlineStr"/>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C004047434</t>
+          <t>C001744771</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C004047434 - PACHECO GUILLEN ABDON JESUS</t>
+          <t>C001744771 - CORTES PEREZ CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -15380,7 +15380,7 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -15434,12 +15434,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C004099658</t>
+          <t>C001703694</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>C004099658 - CHAMBA ORE JULISSA PAMELA</t>
+          <t>C001703694 - OSPINA VARGAS LILIANA MARIBEL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -15465,22 +15465,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S168" t="inlineStr"/>
@@ -15514,7 +15518,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15524,17 +15528,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C004175160</t>
+          <t>C004099658</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>C004175160 - RIVERA CHURA TOMAS</t>
+          <t>C004099658 - CHAMBA ORE JULISSA PAMELA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
@@ -15547,7 +15551,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -15558,9 +15562,21 @@
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr">
         <is>
@@ -15682,7 +15698,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15692,17 +15708,17 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>C004236752</t>
+          <t>C004175160</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>C004236752 - AURORA QUISPE MARLENE</t>
+          <t>C004175160 - RIVERA CHURA TOMAS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
@@ -15715,7 +15731,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -15726,35 +15742,19 @@
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Poco dispuesto</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15876,12 +15876,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>C001635197</t>
+          <t>C001627931</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>C001635197 - INVERSIONES MARKET FOOD E.I.R.L.</t>
+          <t>C001627931 - ESPINOZA CARBAJAL RICHARD OSCAR</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -15912,12 +15912,12 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15928,13 +15928,17 @@
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15966,12 +15970,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>C001627931</t>
+          <t>C001663325</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>C001627931 - ESPINOZA CARBAJAL RICHARD OSCAR</t>
+          <t>C001663325 - PALOMINO VALENZUELA DE FLORES TEODORA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -16018,17 +16022,13 @@
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -16060,12 +16060,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>C001663325</t>
+          <t>C001635197</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>C001663325 - PALOMINO VALENZUELA DE FLORES TEODORA</t>
+          <t>C001635197 - INVERSIONES MARKET FOOD E.I.R.L.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -16096,12 +16096,12 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>C004213339</t>
+          <t>C004188758</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>C004213339 - VARGAS ANCASI BRENDY GERALDINE</t>
+          <t>C004188758 - GONZA CONDORI ANDREA PAMELA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -16375,12 +16375,12 @@
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S178" t="inlineStr"/>
@@ -16391,12 +16391,12 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -16428,12 +16428,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>C004188758</t>
+          <t>C004213339</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>C004188758 - GONZA CONDORI ANDREA PAMELA</t>
+          <t>C004213339 - VARGAS ANCASI BRENDY GERALDINE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S179" t="inlineStr"/>
@@ -16485,12 +16485,12 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16522,12 +16522,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>C004182204</t>
+          <t>C000546428</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C004182204 - VALENCIA ALFARO SANTA CATALINA</t>
+          <t>C000546428 - VILA BALTAZAR ARTURO SIMEON</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -16558,12 +16558,12 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -16612,17 +16612,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C004183586</t>
+          <t>C000547949</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>C004183586 - PEREZ YNGA TERESA LAURA</t>
+          <t>C000547949 - NINAN HUARANCCA DE JARANDILLA LIDIA M.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I181" s="2" t="n">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -16646,21 +16646,9 @@
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
@@ -16702,12 +16690,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>C000546428</t>
+          <t>C001473741</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C000546428 - VILA BALTAZAR ARTURO SIMEON</t>
+          <t>C001473741 - ROQUE FLORES PEDRO ROLANDO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -16738,7 +16726,7 @@
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -16782,7 +16770,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -16792,17 +16780,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C000547949</t>
+          <t>C001219411</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C000547949 - NINAN HUARANCCA DE JARANDILLA LIDIA M.</t>
+          <t>C001219411 - ÑAÑA GONZALES OFELIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I183" s="2" t="n">
@@ -16815,7 +16803,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -16826,9 +16814,21 @@
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
@@ -16870,12 +16870,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001219411</t>
+          <t>C001629425</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C001219411 - ÑAÑA GONZALES OFELIA DEL CARMEN</t>
+          <t>C001629425 - TICONA ROQUE JORDAN YODEMIR</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -16906,7 +16906,7 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001473741</t>
+          <t>C001673326</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001473741 - ROQUE FLORES PEDRO ROLANDO</t>
+          <t>C001673326 - MALLQUE MERCADO DE ÑAÑEZ JUSTA OLGA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -16991,12 +16991,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -17050,12 +17054,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>C001629425</t>
+          <t>C001673997</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>C001629425 - TICONA ROQUE JORDAN YODEMIR</t>
+          <t>C001673997 - VASQUEZ MATAMOROS JASMIN ALEXANDRA</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -17091,7 +17095,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -17324,12 +17328,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>C001673326</t>
+          <t>C001708902</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>C001673326 - MALLQUE MERCADO DE ÑAÑEZ JUSTA OLGA</t>
+          <t>C001708902 - CRUZ CAHUANA ANABEL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -17355,26 +17359,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S189" t="inlineStr"/>
@@ -17418,12 +17418,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C001673997</t>
+          <t>C001737894</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C001673997 - VASQUEZ MATAMOROS JASMIN ALEXANDRA</t>
+          <t>C001737894 - POCCOTAY CARDENAS DIONICIA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -17470,13 +17470,17 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -17508,12 +17512,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C001708902</t>
+          <t>C004049715</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C001708902 - CRUZ CAHUANA ANABEL</t>
+          <t>C004049715 - GALICIO CAMARGO MARISOL KATHERINE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -17549,24 +17553,28 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U191" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17598,12 +17606,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C001737894</t>
+          <t>C001757458</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C001737894 - POCCOTAY CARDENAS DIONICIA</t>
+          <t>C001757458 - RAMIREZ CELESTINO VILMA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -17639,7 +17647,7 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17650,17 +17658,13 @@
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17692,12 +17696,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C001757458</t>
+          <t>C004099750</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C001757458 - RAMIREZ CELESTINO VILMA</t>
+          <t>C004099750 - CORNEJO ROCHA LUCRECIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -17733,12 +17737,12 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S193" t="inlineStr"/>
@@ -17782,12 +17786,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C004049715</t>
+          <t>C004093897</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C004049715 - GALICIO CAMARGO MARISOL KATHERINE</t>
+          <t>C004093897 - BAUTISTA SIHUE LEDISSA BRENDA XIMENA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -17823,28 +17827,24 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17876,12 +17876,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>C004099750</t>
+          <t>C004179580</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>C004099750 - CORNEJO ROCHA LUCRECIA</t>
+          <t>C004179580 - ROJAS TTITO STEVE ALESSANDRO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -17912,17 +17912,17 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S195" t="inlineStr"/>
@@ -17966,12 +17966,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C004093897</t>
+          <t>C004183586</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C004093897 - BAUTISTA SIHUE LEDISSA BRENDA XIMENA</t>
+          <t>C004183586 - PEREZ YNGA TERESA LAURA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -18002,17 +18002,17 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S196" t="inlineStr"/>
@@ -18056,12 +18056,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C004179580</t>
+          <t>C004182204</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>C004179580 - ROJAS TTITO STEVE ALESSANDRO</t>
+          <t>C004182204 - VALENCIA ALFARO SANTA CATALINA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -18092,12 +18092,12 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -18146,12 +18146,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>C004204594</t>
+          <t>C004183873</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>C004204594 - MEJIA BACA ROSA ELENA</t>
+          <t>C004183873 - MARQUINA LA TORRE MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -18182,12 +18182,12 @@
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -18236,12 +18236,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>C004183873</t>
+          <t>C004204594</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>C004183873 - MARQUINA LA TORRE MARIA DEL CARMEN</t>
+          <t>C004204594 - MEJIA BACA ROSA ELENA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -18272,12 +18272,12 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -19422,12 +19422,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C004059896</t>
+          <t>C004181033</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C004059896 - ANTUNEZ ANTUNEZ DE GONZALES ALEJANDRINA</t>
+          <t>C004181033 - CHICOMA CASTANEDA DOMINGA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -19458,12 +19458,12 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -19512,12 +19512,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C001757802</t>
+          <t>C004187067</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C001757802 - MACETAS LUDEÑA ISIDRO ROBERTO</t>
+          <t>C004187067 - VILLAR CORONEL ARACELLY SAMANTHA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -19548,7 +19548,7 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -19558,19 +19558,23 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19602,12 +19606,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C004181033</t>
+          <t>C004059896</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C004181033 - CHICOMA CASTANEDA DOMINGA</t>
+          <t>C004059896 - ANTUNEZ ANTUNEZ DE GONZALES ALEJANDRINA</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -19638,12 +19642,12 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -19692,12 +19696,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C004187067</t>
+          <t>C001757802</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C004187067 - VILLAR CORONEL ARACELLY SAMANTHA</t>
+          <t>C001757802 - MACETAS LUDEÑA ISIDRO ROBERTO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -19728,7 +19732,7 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -19738,23 +19742,19 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20338,12 +20338,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001422888</t>
+          <t>C001657722</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C001422888 - MAMANI CHAVEZ SUJEY BEATRIZ</t>
+          <t>C001657722 - PALACIOS DE JULIAN DIOMILA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -20390,17 +20390,13 @@
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20602,7 +20598,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -20612,17 +20608,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>C001657722</t>
+          <t>C001757318</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>C001657722 - PALACIOS DE JULIAN DIOMILA</t>
+          <t>C001757318 - SANCHEZ REAÑO ROSA DENIS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I225" s="2" t="n">
@@ -20635,7 +20631,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -20646,21 +20642,9 @@
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="R225" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr">
         <is>
@@ -20692,7 +20676,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -20702,17 +20686,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>C001757318</t>
+          <t>C001757443</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>C001757318 - SANCHEZ REAÑO ROSA DENIS</t>
+          <t>C001757443 - JUVENAL DAZA ROBLES</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I226" s="2" t="n">
@@ -20725,7 +20709,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -20736,9 +20720,21 @@
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr">
         <is>
@@ -20780,12 +20776,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C001757443</t>
+          <t>C001758047</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C001757443 - JUVENAL DAZA ROBLES</t>
+          <t>C001758047 - HUAMÁN MATIAS DE ROJAS SONIA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -20821,7 +20817,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -20870,12 +20866,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C001758047</t>
+          <t>C001758229</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C001758047 - HUAMÁN MATIAS DE ROJAS SONIA</t>
+          <t>C001758229 - MOGOLLON ROMERO MILAGROS YAJAIRA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -20906,7 +20902,7 @@
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -20960,12 +20956,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C001758229</t>
+          <t>C001758558</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C001758229 - MOGOLLON ROMERO MILAGROS YAJAIRA</t>
+          <t>C001758558 - INGA DE LA CRUZ MARY NORA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -20996,7 +20992,7 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -21050,12 +21046,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C001758558</t>
+          <t>C004169247</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C001758558 - INGA DE LA CRUZ MARY NORA</t>
+          <t>C004169247 - TOMAS HUAYTA ALEXANDRA VICTORIA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21086,7 +21082,7 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -21140,12 +21136,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C004169247</t>
+          <t>C000542444</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C004169247 - TOMAS HUAYTA ALEXANDRA VICTORIA</t>
+          <t>C000542444 - GELDRES GABRIEL JUANA BARBARA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -21186,7 +21182,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S231" t="inlineStr"/>
@@ -21324,12 +21320,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C000542444</t>
+          <t>C001422888</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C000542444 - GELDRES GABRIEL JUANA BARBARA</t>
+          <t>C001422888 - MAMANI CHAVEZ SUJEY BEATRIZ</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -21365,24 +21361,28 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21692,12 +21692,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C004222842</t>
+          <t>C004044478</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C004222842 - NORIEGA RONDAN ROSARIO STEFANY</t>
+          <t>C004044478 - ALVARADO LOMAS ARTURO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -21733,28 +21733,24 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21876,12 +21872,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001757150</t>
+          <t>C004222842</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001757150 - ORE ROJAS DE PALOMINO HILDA DIONICIA</t>
+          <t>C004222842 - NORIEGA RONDAN ROSARIO STEFANY</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -21912,7 +21908,7 @@
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -21922,19 +21918,23 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21966,12 +21966,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C001757382</t>
+          <t>C001565471</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C001757382 - PALOMINO NAVEROS ISABEL</t>
+          <t>C001565471 - QUISPEHUAMAN ATANACIO DELFINA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -21997,11 +21997,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
@@ -22011,7 +22007,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -22027,12 +22023,12 @@
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22064,12 +22060,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>C004044478</t>
+          <t>C001657626</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C004044478 - ALVARADO LOMAS ARTURO</t>
+          <t>C001657626 - MACHA LAZO VICTORIA JUANA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -22095,34 +22091,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22154,12 +22158,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>C001565471</t>
+          <t>C001675831</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>C001565471 - QUISPEHUAMAN ATANACIO DELFINA</t>
+          <t>C001675831 - MUÑOZ COCHAN JULIA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -22190,7 +22194,7 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
@@ -22248,12 +22252,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>C001657626</t>
+          <t>C001757150</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>C001657626 - MACHA LAZO VICTORIA JUANA</t>
+          <t>C001757150 - ORE ROJAS DE PALOMINO HILDA DIONICIA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -22279,11 +22283,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
@@ -22293,28 +22293,24 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22346,12 +22342,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C001675831</t>
+          <t>C001757382</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>C001675831 - MUÑOZ COCHAN JULIA</t>
+          <t>C001757382 - PALOMINO NAVEROS ISABEL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -22377,17 +22373,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -22403,12 +22403,12 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23250,12 +23250,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C004031784</t>
+          <t>C004097541</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>C004031784 - CASAS MACURI ALEJANDRINA BASILIA</t>
+          <t>C004097541 - JULCA VARGAS SONIA ADAZA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -23281,11 +23281,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
@@ -23295,7 +23291,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -23696,12 +23692,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C004097541</t>
+          <t>C004031784</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>C004097541 - JULCA VARGAS SONIA ADAZA</t>
+          <t>C004031784 - CASAS MACURI ALEJANDRINA BASILIA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -23727,7 +23723,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C001753917</t>
+          <t>C001757064</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C001753917 - MANTILLA GOICOCHEA DE ÑONTOL MARIA SUSAN</t>
+          <t>C001757064 - HUAMAN SOTO MARI AYDE</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -23916,12 +23916,12 @@
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -23932,17 +23932,13 @@
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr"/>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -23974,12 +23970,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>C001757064</t>
+          <t>C001753917</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>C001757064 - HUAMAN SOTO MARI AYDE</t>
+          <t>C001753917 - MANTILLA GOICOCHEA DE ÑONTOL MARIA SUSAN</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -24010,12 +24006,12 @@
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -24026,13 +24022,17 @@
       <c r="S262" t="inlineStr"/>
       <c r="T262" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U262" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V262" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24968,12 +24968,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001692252</t>
+          <t>C001740791</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001692252 - SALAZAR HUARACHI CRHISTIAN JEFFERSON</t>
+          <t>C001740791 - ANYAIPOMA MONTES LEANDRA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25062,12 +25062,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C001762483</t>
+          <t>C001692252</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C001762483 - CCAIHUARI ROJAS OLGA</t>
+          <t>C001692252 - SALAZAR HUARACHI CRHISTIAN JEFFERSON</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -25156,12 +25156,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C001740791</t>
+          <t>C001762483</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C001740791 - ANYAIPOMA MONTES LEANDRA</t>
+          <t>C001762483 - CCAIHUARI ROJAS OLGA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -25612,7 +25612,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -25622,17 +25622,17 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C001398220</t>
+          <t>C001392016</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C001398220 - TERRAZAS DURAND CARMEN EFILIA</t>
+          <t>C001392016 - VELIZ PACHECO NELLY PIEDAD</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I280" s="2" t="n">
@@ -25645,7 +25645,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -25656,19 +25656,35 @@
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
-      <c r="R280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25690,7 +25706,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -25700,17 +25716,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C001408383</t>
+          <t>C001398220</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C001408383 - SACSA ARRIETA LIDIA RENE</t>
+          <t>C001398220 - TERRAZAS DURAND CARMEN EFILIA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I281" s="2" t="n">
@@ -25723,7 +25739,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -25734,21 +25750,9 @@
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q281" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr">
         <is>
@@ -25880,12 +25884,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001392016</t>
+          <t>C001408383</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C001392016 - VELIZ PACHECO NELLY PIEDAD</t>
+          <t>C001408383 - SACSA ARRIETA LIDIA RENE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -25921,28 +25925,24 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr"/>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>

--- a/excel/distribuidora-cunza-s-a_capacitaciones.xlsx
+++ b/excel/distribuidora-cunza-s-a_capacitaciones.xlsx
@@ -1052,12 +1052,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001688415</t>
+          <t>C001616679</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001688415 - MERCEDES CRISTOBAL MOISES BENANCIO</t>
+          <t>C001616679 - MAMANI CHOQUE TERESA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001616679</t>
+          <t>C001736804</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001616679 - MAMANI CHOQUE TERESA</t>
+          <t>C001736804 - PRINCIPE VARGAS LOURDES GERALDINE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001736804</t>
+          <t>C001688415</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001736804 - PRINCIPE VARGAS LOURDES GERALDINE</t>
+          <t>C001688415 - MERCEDES CRISTOBAL MOISES BENANCIO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C004030291</t>
+          <t>C001762685</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C004030291 - PEREZ RUIZ EDUARDO MANUEL</t>
+          <t>C001762685 - ESPINOZA MOSCOSO SILVIA CRISTINA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1722,12 +1722,12 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1738,13 +1738,17 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1780,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001762685</t>
+          <t>C004030291</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001762685 - ESPINOZA MOSCOSO SILVIA CRISTINA</t>
+          <t>C004030291 - PEREZ RUIZ EDUARDO MANUEL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1812,12 +1816,12 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1828,17 +1832,13 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004243560</t>
+          <t>C004166754</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004243560 - CARDENAS HUAMANI JULY MARIVEL</t>
+          <t>C004166754 - AGUADO YAURI MEDARDO RUBEN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004174780</t>
+          <t>C004176403</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C004174780 - LLALLI SOTO CARLA PAMELA</t>
+          <t>C004176403 - RETAMOZO CAMPUZANO DIANA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C004181349</t>
+          <t>C004174780</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C004181349 - AGRO INVERSIONES JHO &amp; MAR S.A.C.</t>
+          <t>C004174780 - LLALLI SOTO CARLA PAMELA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C004166754</t>
+          <t>C004181349</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C004166754 - AGUADO YAURI MEDARDO RUBEN</t>
+          <t>C004181349 - AGRO INVERSIONES JHO &amp; MAR S.A.C.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2266,12 +2266,12 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C004176403</t>
+          <t>C004243560</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C004176403 - RETAMOZO CAMPUZANO DIANA</t>
+          <t>C004243560 - CARDENAS HUAMANI JULY MARIVEL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2356,17 +2356,17 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C004182986</t>
+          <t>C004167596</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C004182986 - AZURZA ESCALANTE JAZMIN BELEN</t>
+          <t>C004167596 - TAPIA LEON LUIS JESUS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2810,7 +2810,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C004183399</t>
+          <t>C004171954</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C004183399 - ASTETE ESCALANTE SANDRA</t>
+          <t>C004171954 - ALHUAY RUIZ WILSON</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2900,12 +2900,12 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001490864</t>
+          <t>C004182986</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001490864 - CACERES GONZALES NIEVES</t>
+          <t>C004182986 - AZURZA ESCALANTE JAZMIN BELEN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2990,12 +2990,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3006,17 +3006,13 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3044,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C000543437</t>
+          <t>C004183399</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C000543437 - CONDORI RAMOS SANTOS</t>
+          <t>C004183399 - ASTETE ESCALANTE SANDRA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3138,12 +3134,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001679735</t>
+          <t>C000543437</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001679735 - CONDORI APAZA MARTHA</t>
+          <t>C000543437 - CONDORI RAMOS SANTOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3174,33 +3170,29 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3214,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3232,17 +3224,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001672463</t>
+          <t>C001490864</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001672463 - CASTAÑEDA CALISAYA EDITH NELLY</t>
+          <t>C001490864 - CACERES GONZALES NIEVES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
@@ -3255,7 +3247,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3266,19 +3258,35 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3502,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001733791</t>
+          <t>C001679735</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001733791 - SALAS ROCA JUANA</t>
+          <t>C001679735 - CONDORI APAZA MARTHA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3530,29 +3538,33 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3586,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3584,17 +3596,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001757160</t>
+          <t>C001672463</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001757160 - BACILIO SALAZAR MILAGROS</t>
+          <t>C001672463 - CASTAÑEDA CALISAYA EDITH NELLY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
@@ -3607,7 +3619,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3618,35 +3630,19 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3678,12 +3674,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001761426</t>
+          <t>C001733791</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001761426 - ROMERO RODRIGUEZ CARMEN ROSE</t>
+          <t>C001733791 - SALAS ROCA JUANA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3714,17 +3710,17 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -3768,12 +3764,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001762738</t>
+          <t>C001757160</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001762738 - PECEROS LOAYZA VICTORIA</t>
+          <t>C001757160 - BACILIO SALAZAR MILAGROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3804,12 +3800,12 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3820,13 +3816,17 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004093873</t>
+          <t>C001761426</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C004093873 - VERA SARMIENTO LUCILA</t>
+          <t>C001761426 - ROMERO RODRIGUEZ CARMEN ROSE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3889,21 +3889,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3952,12 +3948,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C004059353</t>
+          <t>C001762738</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C004059353 - MEDINA NINA DE QUISPE MELIANA</t>
+          <t>C001762738 - PECEROS LOAYZA VICTORIA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3988,7 +3984,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -4406,12 +4402,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C004167596</t>
+          <t>C004093873</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C004167596 - TAPIA LEON LUIS JESUS</t>
+          <t>C004093873 - VERA SARMIENTO LUCILA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4437,7 +4433,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C004171954</t>
+          <t>C004059353</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C004171954 - ALHUAY RUIZ WILSON</t>
+          <t>C004059353 - MEDINA NINA DE QUISPE MELIANA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4532,12 +4532,12 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C004095705</t>
+          <t>C004022016</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C004095705 - CAMA CAPIA ROSALINA</t>
+          <t>C004022016 - GARAMENDI PRADO DE BERROCAL OLINDA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4707,11 +4707,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -4764,7 +4760,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4774,17 +4770,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C004098991</t>
+          <t>C004022179</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C004098991 - RUIZ VALDERRAMA LUZMILA</t>
+          <t>C004022179 - MENDOZA ANDRADE ALVARO JOSE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -4797,7 +4793,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4808,9 +4804,21 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
@@ -4842,7 +4850,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4852,17 +4860,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C004099026</t>
+          <t>C004025463</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C004099026 - BORRAJERO RODRIGO KATHERYN KELLY</t>
+          <t>C004025463 - TRIBIÑOS MUÑOZ LULY</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -4875,7 +4883,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4886,19 +4894,35 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4954,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C004022016</t>
+          <t>C004095705</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C004022016 - GARAMENDI PRADO DE BERROCAL OLINDA</t>
+          <t>C004095705 - CAMA CAPIA ROSALINA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4961,7 +4985,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -5024,12 +5052,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C004022179</t>
+          <t>C001719408</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C004022179 - MENDOZA ANDRADE ALVARO JOSE</t>
+          <t>C001719408 - BUSTAMANTE DELGADO MARIALUISA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5060,12 +5088,12 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5076,13 +5104,17 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5146,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C004025463</t>
+          <t>C001757302</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C004025463 - TRIBIÑOS MUÑOZ LULY</t>
+          <t>C001757302 - CORNEJO ESPIRITU ROSA SUSANA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5155,7 +5187,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5166,17 +5198,13 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5326,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001757302</t>
+          <t>C001696599</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001757302 - CORNEJO ESPIRITU ROSA SUSANA</t>
+          <t>C001696599 - MANCILLA ZAVALETA DE SANCHO SANTOS GLORI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5388,12 +5416,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001719408</t>
+          <t>C004239620</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001719408 - BUSTAMANTE DELGADO MARIALUISA</t>
+          <t>C004239620 - CCASA CHECA OSWALDO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5424,12 +5452,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5440,17 +5468,13 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5506,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C004177436</t>
+          <t>C004236926</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C004177436 - LLOCCLLA JANAMPA FERMIN</t>
+          <t>C004236926 - AQUINO AQUINO JORGE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5576,12 +5600,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C004175227</t>
+          <t>C004177436</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C004175227 - SUNI SANTOYO MARISOL</t>
+          <t>C004177436 - LLOCCLLA JANAMPA FERMIN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5628,13 +5652,17 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5666,12 +5694,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004054830</t>
+          <t>C004175227</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004054830 - RIOS VELA DEIDITH</t>
+          <t>C004175227 - SUNI SANTOYO MARISOL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5702,7 +5730,7 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -5746,7 +5774,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5756,17 +5784,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004239620</t>
+          <t>C004098991</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C004239620 - CCASA CHECA OSWALDO</t>
+          <t>C004098991 - RUIZ VALDERRAMA LUZMILA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -5779,7 +5807,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5790,21 +5818,9 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
@@ -5836,7 +5852,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5846,17 +5862,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C004236926</t>
+          <t>C004099026</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C004236926 - AQUINO AQUINO JORGE</t>
+          <t>C004099026 - BORRAJERO RODRIGO KATHERYN KELLY</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -5869,7 +5885,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5880,35 +5896,19 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001414451</t>
+          <t>C004054830</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001414451 - VALENCIA CHUQUIJA ANSELMA</t>
+          <t>C004054830 - RIOS VELA DEIDITH</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5976,12 +5976,12 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5992,17 +5992,13 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6034,12 +6030,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001662896</t>
+          <t>C001414451</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001662896 - JIMENEZ CASTILLA NAARA LORENA</t>
+          <t>C001414451 - VALENCIA CHUQUIJA ANSELMA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6086,13 +6082,17 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6214,12 +6214,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001696599</t>
+          <t>C001672567</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001696599 - MANCILLA ZAVALETA DE SANCHO SANTOS GLORI</t>
+          <t>C001672567 - SANTANA BARRETO HORLANDINA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6250,7 +6250,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6266,13 +6266,17 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6304,12 +6308,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001672567</t>
+          <t>C001662896</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001672567 - SANTANA BARRETO HORLANDINA</t>
+          <t>C001662896 - JIMENEZ CASTILLA NAARA LORENA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6340,7 +6344,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6356,17 +6360,13 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C001562971</t>
+          <t>C001472910</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C001562971 - ZAVALETA VIDARTE MARIA ELENA</t>
+          <t>C001472910 - COMERCIAL N &amp; M - NIKO Y MECHE S.A.C.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6794,12 +6794,12 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001472910</t>
+          <t>C001562971</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C001472910 - COMERCIAL N &amp; M - NIKO Y MECHE S.A.C.</t>
+          <t>C001562971 - ZAVALETA VIDARTE MARIA ELENA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6888,12 +6888,12 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001682768</t>
+          <t>C001747542</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001682768 - ÑAHUIS MENDOZA MAXIMO</t>
+          <t>C001747542 - SUAVO FLORES RICARDO HIGINIO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7076,33 +7076,29 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7134,12 +7130,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001757782</t>
+          <t>C001738646</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001757782 - ESPINOZA HUAMAN LUCILA</t>
+          <t>C001738646 - CUZCANO CARBONERO MAXIMINA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7175,7 +7171,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7224,12 +7220,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C004048053</t>
+          <t>C001736651</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C004048053 - QUISPE VILLALVA MARTHA</t>
+          <t>C001736651 - QUIROZ CORNEJO LAURA MARGARITA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7260,33 +7256,29 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7318,12 +7310,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001738646</t>
+          <t>C001738624</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001738646 - CUZCANO CARBONERO MAXIMINA</t>
+          <t>C001738624 - PACORA PALACIOS FLOR DE MARIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7364,7 +7356,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
@@ -7408,12 +7400,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001736651</t>
+          <t>C001714577</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001736651 - QUIROZ CORNEJO LAURA MARGARITA</t>
+          <t>C001714577 - GUERRA POVEDA PETRONILA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7449,7 +7441,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7498,12 +7490,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001738624</t>
+          <t>C001682768</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001738624 - PACORA PALACIOS FLOR DE MARIA</t>
+          <t>C001682768 - ÑAHUIS MENDOZA MAXIMO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7534,29 +7526,33 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7588,12 +7584,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001747542</t>
+          <t>C001729220</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001747542 - SUAVO FLORES RICARDO HIGINIO</t>
+          <t>C001729220 - MORALES OSCO RICHARD GUMERCINDO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7624,17 +7620,17 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S79" t="inlineStr"/>
@@ -7768,12 +7764,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C001714577</t>
+          <t>C004032353</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C001714577 - GUERRA POVEDA PETRONILA</t>
+          <t>C004032353 - FERNANDEZ ILATOMA MARIBEL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7804,7 +7800,7 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -7858,12 +7854,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C001729220</t>
+          <t>C004048053</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C001729220 - MORALES OSCO RICHARD GUMERCINDO</t>
+          <t>C004048053 - QUISPE VILLALVA MARTHA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7904,19 +7900,23 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C004166585</t>
+          <t>C001757782</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C004166585 - RESURRECCION YANAVILCA DANIELA ARIANA</t>
+          <t>C001757782 - ESPINOZA HUAMAN LUCILA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7984,7 +7984,7 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C004032353</t>
+          <t>C004166585</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C004032353 - FERNANDEZ ILATOMA MARIBEL</t>
+          <t>C004166585 - RESURRECCION YANAVILCA DANIELA ARIANA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001476385</t>
+          <t>C001741233</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C001476385 - CANDELA CASAS JESUS ADELA</t>
+          <t>C001741233 - SUPO ROMAN DE MENDOZA JULIA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8905,28 +8905,24 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8958,12 +8954,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001441810</t>
+          <t>C001635189</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C001441810 - SOSA FERNANDEZ MARIA ROSARIO</t>
+          <t>C001635189 - SIFUENTES ESTRADA DOMITILA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8999,12 +8995,12 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S94" t="inlineStr"/>
@@ -9015,12 +9011,12 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9052,12 +9048,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001635189</t>
+          <t>C001623779</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C001635189 - SIFUENTES ESTRADA DOMITILA</t>
+          <t>C001623779 - HUARHUACHI HUACRE MARIA LUZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9088,7 +9084,7 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -9104,17 +9100,13 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9138,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001623779</t>
+          <t>C001476385</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C001623779 - HUARHUACHI HUACRE MARIA LUZ</t>
+          <t>C001476385 - CANDELA CASAS JESUS ADELA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9182,29 +9174,33 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9236,12 +9232,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001741233</t>
+          <t>C001441810</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001741233 - SUPO ROMAN DE MENDOZA JULIA</t>
+          <t>C001441810 - SOSA FERNANDEZ MARIA ROSARIO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9277,24 +9273,28 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9326,12 +9326,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C004029938</t>
+          <t>C001749942</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C004029938 - BETO TEC STORE E.I.R.L.</t>
+          <t>C001749942 - AQUISE HUACANI FLOR TRINIDAD</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9362,7 +9362,7 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -9378,17 +9378,13 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9420,12 +9416,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C004099849</t>
+          <t>C001757080</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C004099849 - VICENTE HUAMANI RICARDO</t>
+          <t>C001757080 - ROMERO SAMANEZ DE QUISPE ROSA AMABILIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9456,33 +9452,29 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9514,12 +9506,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C004190558</t>
+          <t>C004029938</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C004190558 - PADILLA AMIA CRISTINA ELISA</t>
+          <t>C004029938 - BETO TEC STORE E.I.R.L.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9550,12 +9542,12 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9571,12 +9563,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9608,12 +9600,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C004183653</t>
+          <t>C004099849</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C004183653 - TORRES ROMANI LUZ ESTHER</t>
+          <t>C004099849 - VICENTE HUAMANI RICARDO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9702,12 +9694,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C004180800</t>
+          <t>C004183653</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C004180800 - CONDORI UNUCUECA MIRTHA CAROLINA</t>
+          <t>C004183653 - TORRES ROMANI LUZ ESTHER</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9738,12 +9730,12 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -9759,12 +9751,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9796,12 +9788,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C004207454</t>
+          <t>C004190558</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C004207454 - TUMBA GOMEZ LUCY CARMEN</t>
+          <t>C004190558 - PADILLA AMIA CRISTINA ELISA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9837,7 +9829,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -9890,12 +9882,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C000511786</t>
+          <t>C004207454</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C000511786 - NARAZA PRADO NATALIA</t>
+          <t>C004207454 - TUMBA GOMEZ LUCY CARMEN</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9931,7 +9923,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -9984,12 +9976,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C000427085</t>
+          <t>C004180800</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C000427085 - ROMERO ALEJANDRO NEDA</t>
+          <t>C004180800 - CONDORI UNUCUECA MIRTHA CAROLINA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10020,12 +10012,12 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -10041,12 +10033,12 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10078,12 +10070,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C000544553</t>
+          <t>C000511786</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C000544553 - CHIRINOS MORIANO ALICIA</t>
+          <t>C000511786 - NARAZA PRADO NATALIA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10114,12 +10106,12 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -10135,12 +10127,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10164,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C001474012</t>
+          <t>C000427085</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C001474012 - RAMOS HUAYTA SOFIA ESPERANZA</t>
+          <t>C000427085 - ROMERO ALEJANDRO NEDA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10213,12 +10205,12 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S107" t="inlineStr"/>
@@ -10229,12 +10221,12 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10266,12 +10258,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001398120</t>
+          <t>C000544553</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001398120 - NOSTADES QUISPE KAREN JANNET</t>
+          <t>C000544553 - CHIRINOS MORIANO ALICIA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10318,13 +10310,17 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10352,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C001525506</t>
+          <t>C001398120</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C001525506 - ALLCCA TINTAYA AMBROCIA</t>
+          <t>C001398120 - NOSTADES QUISPE KAREN JANNET</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10392,33 +10388,29 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10450,12 +10442,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C001710988</t>
+          <t>C001474012</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C001710988 - VERDI CRUZ NELY NORMA</t>
+          <t>C001474012 - RAMOS HUAYTA SOFIA ESPERANZA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10486,29 +10478,33 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10540,12 +10536,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001717374</t>
+          <t>C001525506</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C001717374 - PAREDES PAREDES DE HANCCO RAIMONDA</t>
+          <t>C001525506 - ALLCCA TINTAYA AMBROCIA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10581,24 +10577,28 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -10630,17 +10630,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C001703308</t>
+          <t>C001717374</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C001703308 - VILA VILA EMILY SINDY</t>
+          <t>C001717374 - PAREDES PAREDES DE HANCCO RAIMONDA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10664,23 +10664,31 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10710,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10712,17 +10720,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C001749942</t>
+          <t>C001703308</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C001749942 - AQUISE HUACANI FLOR TRINIDAD</t>
+          <t>C001703308 - VILA VILA EMILY SINDY</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
@@ -10735,7 +10743,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10746,31 +10754,23 @@
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10802,12 +10802,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C001757080</t>
+          <t>C001710988</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C001757080 - ROMERO SAMANEZ DE QUISPE ROSA AMABILIA</t>
+          <t>C001710988 - VERDI CRUZ NELY NORMA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10838,17 +10838,17 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S114" t="inlineStr"/>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C004200844</t>
+          <t>C004170770</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C004200844 - CUYA HUACHUHUILLCA FORTUNATA</t>
+          <t>C004170770 - GOMEZ TINTAYA JOSE WILFREDO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10928,7 +10928,7 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C004207921</t>
+          <t>C004200844</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C004207921 - ESTRELLA ALDERETE MAGALI SONIA</t>
+          <t>C004200844 - CUYA HUACHUHUILLCA FORTUNATA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11022,12 +11022,12 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -11038,13 +11038,17 @@
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11080,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C004094278</t>
+          <t>C004207921</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C004094278 - QUISPE BAEZ ELSA</t>
+          <t>C004207921 - ESTRELLA ALDERETE MAGALI SONIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11112,12 +11116,12 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -11128,17 +11132,13 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11170,12 +11170,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C004170770</t>
+          <t>C004094278</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C004170770 - GOMEZ TINTAYA JOSE WILFREDO</t>
+          <t>C004094278 - QUISPE BAEZ ELSA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11206,7 +11206,7 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11996,17 +11996,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C004167725</t>
+          <t>C001737021</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C004167725 - MENDOZA TELLO ROBERTA JULIA</t>
+          <t>C001737021 - VALLEJOS JINEZ GUILIANA ELVIRA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -12030,35 +12030,19 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -12090,12 +12074,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C004165557</t>
+          <t>C001736451</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C004165557 - VELASQUEZ MERCADO EVELYN</t>
+          <t>C001736451 - CAILLAHUA FUENTES MARCELINA VALERIANA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12126,7 +12110,7 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -12142,13 +12126,17 @@
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12158,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12180,17 +12168,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C001737021</t>
+          <t>C001757996</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C001737021 - VALLEJOS JINEZ GUILIANA ELVIRA</t>
+          <t>C001757996 - INGARUCA RIVAS LESLIE MILAGROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
@@ -12203,7 +12191,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -12214,9 +12202,21 @@
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
@@ -12258,12 +12258,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001736451</t>
+          <t>C001755476</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>C001736451 - CAILLAHUA FUENTES MARCELINA VALERIANA</t>
+          <t>C001755476 - HUAMAN PEÑALOZA HILDA YSABEL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12294,7 +12294,7 @@
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -12352,12 +12352,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C001757996</t>
+          <t>C004045205</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C001757996 - INGARUCA RIVAS LESLIE MILAGROS</t>
+          <t>C004045205 - BENDITA QUISPE NATI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12388,12 +12388,12 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -12442,12 +12442,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C001755476</t>
+          <t>C004167725</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>C001755476 - HUAMAN PEÑALOZA HILDA YSABEL</t>
+          <t>C004167725 - MENDOZA TELLO ROBERTA JULIA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -12478,17 +12478,17 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S132" t="inlineStr"/>
@@ -12630,12 +12630,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C004045205</t>
+          <t>C004165557</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>C004045205 - BENDITA QUISPE NATI</t>
+          <t>C004165557 - VELASQUEZ MERCADO EVELYN</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -12666,7 +12666,7 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -17132,17 +17132,17 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C001757852</t>
+          <t>C004023132</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C001757852 - SARAVIA RIVERA CARLOS FERNANDO</t>
+          <t>C004023132 - TOCTO LLACSAHUANGA DELIXABEL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I183" s="2" t="n">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -17166,31 +17166,23 @@
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17222,12 +17214,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001757933</t>
+          <t>C001757852</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C001757933 - CHUCO MORENO JUAN PABLO</t>
+          <t>C001757852 - SARAVIA RIVERA CARLOS FERNANDO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -17274,17 +17266,13 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17316,12 +17304,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001758571</t>
+          <t>C001757933</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001758571 - CHUMPITAZ CULQUICONDOR LUIS ENRIQUE</t>
+          <t>C001757933 - CHUCO MORENO JUAN PABLO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -17347,21 +17335,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -17372,13 +17356,17 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17410,12 +17398,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>C001679814</t>
+          <t>C001758571</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>C001679814 - ANDRADE YABARINO ALEXANDRA FABIOLA</t>
+          <t>C001758571 - CHUMPITAZ CULQUICONDOR LUIS ENRIQUE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -17441,38 +17429,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17504,12 +17492,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C000423530</t>
+          <t>C001679814</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>C000423530 - CAVERO BENITES SERGIO</t>
+          <t>C001679814 - ANDRADE YABARINO ALEXANDRA FABIOLA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -17540,17 +17528,17 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S187" t="inlineStr"/>
@@ -17588,7 +17576,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -17598,17 +17586,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>C000423757</t>
+          <t>C000423530</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>C000423757 - ARMACANQUI FLORES ETELVINA</t>
+          <t>C000423530 - CAVERO BENITES SERGIO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I188" s="2" t="n">
@@ -17621,7 +17609,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -17632,9 +17620,21 @@
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -17680,17 +17680,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>C000424427</t>
+          <t>C000423757</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>C000424427 - PAMPAMALLCO APAZA DE TOLEDO LEONOR</t>
+          <t>C000423757 - ARMACANQUI FLORES ETELVINA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I189" s="2" t="n">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -17714,21 +17714,9 @@
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr">
         <is>
@@ -17764,7 +17752,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -17774,17 +17762,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C004023132</t>
+          <t>C000424427</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C004023132 - TOCTO LLACSAHUANGA DELIXABEL</t>
+          <t>C000424427 - PAMPAMALLCO APAZA DE TOLEDO LEONOR</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I190" s="2" t="n">
@@ -17797,7 +17785,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -17808,9 +17796,21 @@
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr">
         <is>
@@ -17819,12 +17819,12 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19792,7 +19792,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -19802,17 +19802,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C004167957</t>
+          <t>C004175160</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C004167957 - ZUÑIGA GONZALES BRIGITTE ARACELI</t>
+          <t>C004175160 - RIVERA CHURA TOMAS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I212" s="2" t="n">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -19836,31 +19836,23 @@
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>Más productos disponibles</t>
-        </is>
-      </c>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19874,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -19892,17 +19884,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C004175160</t>
+          <t>C004167957</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C004175160 - RIVERA CHURA TOMAS</t>
+          <t>C004167957 - ZUÑIGA GONZALES BRIGITTE ARACELI</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I213" s="2" t="n">
@@ -19915,7 +19907,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -19926,23 +19918,31 @@
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Más productos disponibles</t>
+        </is>
+      </c>
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20346,12 +20346,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001635197</t>
+          <t>C001663325</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>C001635197 - INVERSIONES MARKET FOOD E.I.R.L.</t>
+          <t>C001663325 - PALOMINO VALENZUELA DE FLORES TEODORA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -20382,12 +20382,12 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -20440,12 +20440,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C001663325</t>
+          <t>C001635197</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>C001663325 - PALOMINO VALENZUELA DE FLORES TEODORA</t>
+          <t>C001635197 - INVERSIONES MARKET FOOD E.I.R.L.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -20476,12 +20476,12 @@
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -21172,12 +21172,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C001219411</t>
+          <t>C001473741</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C001219411 - ÑAÑA GONZALES OFELIA DEL CARMEN</t>
+          <t>C001473741 - ROQUE FLORES PEDRO ROLANDO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -21208,7 +21208,7 @@
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -21224,17 +21224,13 @@
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21266,12 +21262,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C001473741</t>
+          <t>C001629425</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C001473741 - ROQUE FLORES PEDRO ROLANDO</t>
+          <t>C001629425 - TICONA ROQUE JORDAN YODEMIR</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -21356,12 +21352,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C001629425</t>
+          <t>C001219411</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C001629425 - TICONA ROQUE JORDAN YODEMIR</t>
+          <t>C001219411 - ÑAÑA GONZALES OFELIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -21392,7 +21388,7 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -21408,13 +21404,17 @@
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U229" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21446,12 +21446,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C001673326</t>
+          <t>C001737894</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C001673326 - MALLQUE MERCADO DE ÑAÑEZ JUSTA OLGA</t>
+          <t>C001737894 - POCCOTAY CARDENAS DIONICIA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21477,21 +21477,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
@@ -21507,12 +21503,12 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21544,12 +21540,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C001673997</t>
+          <t>C001692492</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C001673997 - VASQUEZ MATAMOROS JASMIN ALEXANDRA</t>
+          <t>C001692492 - ARTEAGA CONTRERAS NANCY JUANA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -21634,12 +21630,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C001689686</t>
+          <t>C001708902</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C001689686 - GALLEGOS GUISADO CARMEN ROSA</t>
+          <t>C001708902 - CRUZ CAHUANA ANABEL</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -21675,12 +21671,12 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S232" t="inlineStr"/>
@@ -21691,12 +21687,12 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21728,12 +21724,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001692492</t>
+          <t>C001673326</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001692492 - ARTEAGA CONTRERAS NANCY JUANA</t>
+          <t>C001673326 - MALLQUE MERCADO DE ÑAÑEZ JUSTA OLGA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -21759,17 +21755,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -21780,13 +21780,17 @@
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U233" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21818,12 +21822,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001708902</t>
+          <t>C001673997</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>C001708902 - CRUZ CAHUANA ANABEL</t>
+          <t>C001673997 - VASQUEZ MATAMOROS JASMIN ALEXANDRA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -21859,28 +21863,24 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21912,12 +21912,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C001757458</t>
+          <t>C001689686</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>C001757458 - RAMIREZ CELESTINO VILMA</t>
+          <t>C001689686 - GALLEGOS GUISADO CARMEN ROSA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -21953,24 +21953,28 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U235" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22002,12 +22006,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C001737894</t>
+          <t>C004049715</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>C001737894 - POCCOTAY CARDENAS DIONICIA</t>
+          <t>C004049715 - GALICIO CAMARGO MARISOL KATHERINE</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -22043,7 +22047,7 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -22059,12 +22063,12 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22096,12 +22100,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C004049715</t>
+          <t>C004093897</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C004049715 - GALICIO CAMARGO MARISOL KATHERINE</t>
+          <t>C004093897 - BAUTISTA SIHUE LEDISSA BRENDA XIMENA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -22137,12 +22141,12 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S237" t="inlineStr"/>
@@ -22153,12 +22157,12 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22190,12 +22194,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C004093897</t>
+          <t>C001757458</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C004093897 - BAUTISTA SIHUE LEDISSA BRENDA XIMENA</t>
+          <t>C001757458 - RAMIREZ CELESTINO VILMA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22231,28 +22235,24 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -23012,12 +23012,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C001756025</t>
+          <t>C001732987</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C001756025 - RODRIGUEZ RIVERA GUILLERMO ALBERTO</t>
+          <t>C001732987 - PALOMINO SULCA CARMEN ADA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -23069,12 +23069,12 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23106,12 +23106,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C001758520</t>
+          <t>C004047842</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>C001758520 - GARCIA RIOFRIO RUBY YASMINE</t>
+          <t>C004047842 - QUISPE AUCCATINCO MARTHA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -23158,17 +23158,13 @@
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -23200,12 +23196,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>C001732987</t>
+          <t>C001756025</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>C001732987 - PALOMINO SULCA CARMEN ADA</t>
+          <t>C001756025 - RODRIGUEZ RIVERA GUILLERMO ALBERTO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -23257,12 +23253,12 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23294,12 +23290,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>C004047842</t>
+          <t>C001758520</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>C004047842 - QUISPE AUCCATINCO MARTHA</t>
+          <t>C001758520 - GARCIA RIOFRIO RUBY YASMINE</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -23335,7 +23331,7 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -23346,13 +23342,17 @@
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23944,12 +23944,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C004181033</t>
+          <t>C001757802</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>C004181033 - CHICOMA CASTANEDA DOMINGA</t>
+          <t>C001757802 - MACETAS LUDEÑA ISIDRO ROBERTO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -23980,7 +23980,7 @@
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
@@ -23990,23 +23990,19 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S257" t="inlineStr"/>
       <c r="T257" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -24038,12 +24034,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C004187067</t>
+          <t>C004181033</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>C004187067 - VILLAR CORONEL ARACELLY SAMANTHA</t>
+          <t>C004181033 - CHICOMA CASTANEDA DOMINGA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -24074,7 +24070,7 @@
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
@@ -24095,12 +24091,12 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24132,12 +24128,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C001757802</t>
+          <t>C004187067</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>C001757802 - MACETAS LUDEÑA ISIDRO ROBERTO</t>
+          <t>C004187067 - VILLAR CORONEL ARACELLY SAMANTHA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -24168,7 +24164,7 @@
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
@@ -24178,19 +24174,23 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U259" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -24772,7 +24772,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -24782,17 +24782,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C001757318</t>
+          <t>C001650221</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C001757318 - SANCHEZ REAÑO ROSA DENIS</t>
+          <t>C001650221 - OLARTE MORALES JESUS JAVIER</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I266" s="2" t="n">
@@ -24805,7 +24805,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -24816,19 +24816,35 @@
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
-      <c r="R266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U266" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24860,12 +24876,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C001757443</t>
+          <t>C001657722</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>C001757443 - JUVENAL DAZA ROBLES</t>
+          <t>C001657722 - PALACIOS DE JULIAN DIOMILA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -24901,7 +24917,7 @@
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -24950,12 +24966,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>C001758047</t>
+          <t>C001745164</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>C001758047 - HUAMÁN MATIAS DE ROJAS SONIA</t>
+          <t>C001745164 - RIVERA JACOBO EDWIN JENSHON</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -24986,12 +25002,12 @@
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -25002,13 +25018,17 @@
       <c r="S268" t="inlineStr"/>
       <c r="T268" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25030,7 +25050,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -25040,17 +25060,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C001758229</t>
+          <t>C001757318</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>C001758229 - MOGOLLON ROMERO MILAGROS YAJAIRA</t>
+          <t>C001757318 - SANCHEZ REAÑO ROSA DENIS</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I269" s="2" t="n">
@@ -25063,7 +25083,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -25074,35 +25094,19 @@
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr">
-        <is>
-          <t>Nada dispuesto</t>
-        </is>
-      </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R269" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr"/>
       <c r="V269" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25134,12 +25138,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C001758558</t>
+          <t>C001757443</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>C001758558 - INGA DE LA CRUZ MARY NORA</t>
+          <t>C001757443 - JUVENAL DAZA ROBLES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -25170,12 +25174,12 @@
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -25186,17 +25190,13 @@
       <c r="S270" t="inlineStr"/>
       <c r="T270" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr"/>
       <c r="V270" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25228,12 +25228,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C001745164</t>
+          <t>C001758047</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>C001745164 - RIVERA JACOBO EDWIN JENSHON</t>
+          <t>C001758047 - HUAMÁN MATIAS DE ROJAS SONIA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -25264,12 +25264,12 @@
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -25280,17 +25280,13 @@
       <c r="S271" t="inlineStr"/>
       <c r="T271" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr"/>
       <c r="V271" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25322,12 +25318,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C001650221</t>
+          <t>C001758229</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>C001650221 - OLARTE MORALES JESUS JAVIER</t>
+          <t>C001758229 - MOGOLLON ROMERO MILAGROS YAJAIRA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -25358,7 +25354,7 @@
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
@@ -25379,12 +25375,12 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25416,12 +25412,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001657722</t>
+          <t>C001758558</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001657722 - PALACIOS DE JULIAN DIOMILA</t>
+          <t>C001758558 - INGA DE LA CRUZ MARY NORA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25452,12 +25448,12 @@
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -25468,13 +25464,17 @@
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25596,12 +25596,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C000542444</t>
+          <t>C001366019</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C000542444 - GELDRES GABRIEL JUANA BARBARA</t>
+          <t>C001366019 - CONDE CABANA MARIELA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -25632,7 +25632,7 @@
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S275" t="inlineStr"/>
@@ -25653,12 +25653,12 @@
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C001366019</t>
+          <t>C001422888</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>C001366019 - CONDE CABANA MARIELA</t>
+          <t>C001422888 - MAMANI CHAVEZ SUJEY BEATRIZ</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -25726,12 +25726,12 @@
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -25784,12 +25784,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C001422888</t>
+          <t>C000542444</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>C001422888 - MAMANI CHAVEZ SUJEY BEATRIZ</t>
+          <t>C000542444 - GELDRES GABRIEL JUANA BARBARA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -25825,12 +25825,12 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S277" t="inlineStr"/>
@@ -25841,12 +25841,12 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25968,12 +25968,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C001655201</t>
+          <t>C004239859</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C001655201 - FIGUEROA RODAS JOSE ALFREDO</t>
+          <t>C004239859 - CONDORI LLAMOCCA CLAUDIA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -25999,21 +25999,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -26024,13 +26020,17 @@
       <c r="S279" t="inlineStr"/>
       <c r="T279" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26062,12 +26062,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C004044478</t>
+          <t>C004222842</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C004044478 - ALVARADO LOMAS ARTURO</t>
+          <t>C004222842 - NORIEGA RONDAN ROSARIO STEFANY</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -26103,12 +26103,12 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S280" t="inlineStr"/>
@@ -26156,12 +26156,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C001757150</t>
+          <t>C004180791</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C001757150 - ORE ROJAS DE PALOMINO HILDA DIONICIA</t>
+          <t>C004180791 - MARTINEZ ANDAMAYO ROSALINA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -26202,19 +26202,23 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26246,12 +26250,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C001757382</t>
+          <t>C004044478</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C001757382 - PALOMINO NAVEROS ISABEL</t>
+          <t>C004044478 - ALVARADO LOMAS ARTURO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -26277,11 +26281,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -26307,12 +26307,12 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V282" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26344,12 +26344,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C004180791</t>
+          <t>C001675831</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C004180791 - MARTINEZ ANDAMAYO ROSALINA</t>
+          <t>C001675831 - MUÑOZ COCHAN JULIA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -26385,12 +26385,12 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S283" t="inlineStr"/>
@@ -26438,12 +26438,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C004239859</t>
+          <t>C001657626</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>C004239859 - CONDORI LLAMOCCA CLAUDIA</t>
+          <t>C001657626 - MACHA LAZO VICTORIA JUANA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -26469,12 +26469,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
@@ -26484,7 +26488,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S284" t="inlineStr"/>
@@ -26532,12 +26536,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C004222842</t>
+          <t>C001757150</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>C004222842 - NORIEGA RONDAN ROSARIO STEFANY</t>
+          <t>C001757150 - ORE ROJAS DE PALOMINO HILDA DIONICIA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -26568,7 +26572,7 @@
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
@@ -26578,23 +26582,19 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S285" t="inlineStr"/>
       <c r="T285" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr"/>
       <c r="V285" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26626,12 +26626,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C001657626</t>
+          <t>C001757382</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>C001657626 - MACHA LAZO VICTORIA JUANA</t>
+          <t>C001757382 - PALOMINO NAVEROS ISABEL</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -26666,17 +26666,17 @@
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S286" t="inlineStr"/>
@@ -26687,12 +26687,12 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26724,12 +26724,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C001675831</t>
+          <t>C001565471</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>C001675831 - MUÑOZ COCHAN JULIA</t>
+          <t>C001565471 - QUISPEHUAMAN ATANACIO DELFINA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -26760,7 +26760,7 @@
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
@@ -26808,7 +26808,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -26818,17 +26818,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C001565471</t>
+          <t>C001485270</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>C001565471 - QUISPEHUAMAN ATANACIO DELFINA</t>
+          <t>C001485270 - CHUMACERO CORDOVA ADALY ISABEL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I288" s="2" t="n">
@@ -26841,7 +26841,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -26852,21 +26852,9 @@
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
       <c r="S288" t="inlineStr"/>
       <c r="T288" t="inlineStr">
         <is>
@@ -26902,7 +26890,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -26912,17 +26900,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>C001485270</t>
+          <t>C001389266</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>C001485270 - CHUMACERO CORDOVA ADALY ISABEL</t>
+          <t>C001389266 - PISCO SANCHEZ MARIA ROSENDA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I289" s="2" t="n">
@@ -26935,7 +26923,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -26946,9 +26934,21 @@
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
-      <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="inlineStr"/>
-      <c r="R289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
       <c r="S289" t="inlineStr"/>
       <c r="T289" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -26994,17 +26994,17 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>C001389266</t>
+          <t>C001334121</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>C001389266 - PISCO SANCHEZ MARIA ROSENDA</t>
+          <t>C001334121 - PORTILLA PALMA DE FLORES EUMELIA MARINA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I290" s="2" t="n">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -27028,21 +27028,9 @@
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr">
-        <is>
-          <t>Poco dispuesto</t>
-        </is>
-      </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R290" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr">
         <is>
@@ -27078,7 +27066,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -27088,17 +27076,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C001334121</t>
+          <t>C000508388</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>C001334121 - PORTILLA PALMA DE FLORES EUMELIA MARINA</t>
+          <t>C000508388 - ROBLES MAMANI DE ARTEAGA MARIA CASIMIRA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I291" s="2" t="n">
@@ -27111,7 +27099,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -27122,23 +27110,31 @@
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr"/>
-      <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="inlineStr"/>
-      <c r="R291" t="inlineStr"/>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S291" t="inlineStr"/>
       <c r="T291" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr"/>
       <c r="V291" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27170,12 +27166,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C000508388</t>
+          <t>C000507674</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C000508388 - ROBLES MAMANI DE ARTEAGA MARIA CASIMIRA</t>
+          <t>C000507674 - FERNANDEZ PANIAGUA VALERIANO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -27206,12 +27202,12 @@
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -27260,12 +27256,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C000507674</t>
+          <t>C000511760</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>C000507674 - FERNANDEZ PANIAGUA VALERIANO</t>
+          <t>C000511760 - CORREA TAMAYO CARMEN JOSEFINA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -27306,19 +27302,23 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27350,12 +27350,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C000511760</t>
+          <t>C001655201</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>C000511760 - CORREA TAMAYO CARMEN JOSEFINA</t>
+          <t>C001655201 - FIGUEROA RODAS JOSE ALFREDO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -27381,12 +27381,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr"/>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
@@ -27396,23 +27400,19 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S294" t="inlineStr"/>
       <c r="T294" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27726,12 +27726,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001757064</t>
+          <t>C004031784</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>C001757064 - HUAMAN SOTO MARI AYDE</t>
+          <t>C004031784 - CASAS MACURI ALEJANDRINA BASILIA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -27757,17 +27757,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -27778,13 +27782,17 @@
       <c r="S298" t="inlineStr"/>
       <c r="T298" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27816,12 +27824,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001753917</t>
+          <t>C004066085</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>C001753917 - MANTILLA GOICOCHEA DE ÑONTOL MARIA SUSAN</t>
+          <t>C004066085 - TAIPE CAHUANA CARMELA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -27852,12 +27860,12 @@
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -27868,17 +27876,13 @@
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr"/>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27904,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -27910,17 +27914,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>C004031784</t>
+          <t>C004165327</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>C004031784 - CASAS MACURI ALEJANDRINA BASILIA</t>
+          <t>C004165327 - MENDOZA ORTIZ OSCAR JHONNY</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I300" s="2" t="n">
@@ -27933,7 +27937,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -27941,28 +27945,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R300" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr">
         <is>
@@ -28008,12 +27996,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>C004066085</t>
+          <t>C004097541</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>C004066085 - TAIPE CAHUANA CARMELA</t>
+          <t>C004097541 - JULCA VARGAS SONIA ADAZA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -28044,12 +28032,12 @@
       <c r="O301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -28060,13 +28048,17 @@
       <c r="S301" t="inlineStr"/>
       <c r="T301" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28080,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -28098,17 +28090,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>C004165327</t>
+          <t>C004174131</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>C004165327 - MENDOZA ORTIZ OSCAR JHONNY</t>
+          <t>C004174131 - RAMOS HIDALGO SOSIMA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I302" s="2" t="n">
@@ -28121,7 +28113,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -28132,9 +28124,21 @@
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr"/>
-      <c r="P302" t="inlineStr"/>
-      <c r="Q302" t="inlineStr"/>
-      <c r="R302" t="inlineStr"/>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
       <c r="S302" t="inlineStr"/>
       <c r="T302" t="inlineStr">
         <is>
@@ -28143,12 +28147,12 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V302" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28180,12 +28184,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>C004097541</t>
+          <t>C004174404</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>C004097541 - JULCA VARGAS SONIA ADAZA</t>
+          <t>C004174404 - RAMIREZ FERNANDEZ DE JOYA ELDA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -28216,33 +28220,29 @@
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S303" t="inlineStr"/>
       <c r="T303" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28274,12 +28274,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>C004174131</t>
+          <t>C001646326</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>C004174131 - RAMOS HIDALGO SOSIMA</t>
+          <t>C001646326 - ROMAN CONTRERAS RIZO PATRON</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -28320,7 +28320,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S304" t="inlineStr"/>
@@ -28368,12 +28368,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>C004174404</t>
+          <t>C001753917</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>C004174404 - RAMIREZ FERNANDEZ DE JOYA ELDA</t>
+          <t>C001753917 - MANTILLA GOICOCHEA DE ÑONTOL MARIA SUSAN</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -28404,29 +28404,33 @@
       <c r="O305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S305" t="inlineStr"/>
       <c r="T305" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28458,12 +28462,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>C001646326</t>
+          <t>C001757064</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>C001646326 - ROMAN CONTRERAS RIZO PATRON</t>
+          <t>C001757064 - HUAMAN SOTO MARI AYDE</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -28499,28 +28503,24 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S306" t="inlineStr"/>
       <c r="T306" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr"/>
       <c r="V306" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28552,12 +28552,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>C004044469</t>
+          <t>C001757324</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>C004044469 - PEREZ DUPUY MAXIMO SEVERIANO</t>
+          <t>C001757324 - OSORIO CURI NELIDA LEOPOLDA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -28588,17 +28588,17 @@
       <c r="O307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S307" t="inlineStr"/>
@@ -28740,12 +28740,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C001757324</t>
+          <t>C004044469</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>C001757324 - OSORIO CURI NELIDA LEOPOLDA</t>
+          <t>C004044469 - PEREZ DUPUY MAXIMO SEVERIANO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -28776,17 +28776,17 @@
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S309" t="inlineStr"/>
@@ -28834,12 +28834,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>C001409695</t>
+          <t>C001623430</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>C001409695 - ACHAHUANCO ADAME YOLANDA</t>
+          <t>C001623430 - LAURA QUISPE ROSA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -28870,12 +28870,12 @@
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -28886,17 +28886,13 @@
       <c r="S310" t="inlineStr"/>
       <c r="T310" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr"/>
       <c r="V310" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28928,12 +28924,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C001623430</t>
+          <t>C001409695</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>C001623430 - LAURA QUISPE ROSA</t>
+          <t>C001409695 - ACHAHUANCO ADAME YOLANDA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -28964,12 +28960,12 @@
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -28980,13 +28976,17 @@
       <c r="S311" t="inlineStr"/>
       <c r="T311" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29018,12 +29018,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>C001740791</t>
+          <t>C001670096</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>C001740791 - ANYAIPOMA MONTES LEANDRA</t>
+          <t>C001670096 - GROUP ONE SAC</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -29054,7 +29054,7 @@
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -29112,17 +29112,17 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>C001744346</t>
+          <t>C004184900</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>C001744346 - SANCHEZ CABALLERO SANDRA JULIANA</t>
+          <t>C004184900 - TORRES GONGORA CALISTO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I313" s="2" t="n">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -29146,35 +29146,19 @@
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
       <c r="O313" t="inlineStr"/>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q313" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R313" t="inlineStr">
-        <is>
-          <t>Más confianza en la entrega</t>
-        </is>
-      </c>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
+      <c r="R313" t="inlineStr"/>
       <c r="S313" t="inlineStr"/>
       <c r="T313" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr"/>
       <c r="V313" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29206,12 +29190,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>C001670096</t>
+          <t>C004188961</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>C001670096 - GROUP ONE SAC</t>
+          <t>C004188961 - VELARDE ASCONA DELIA ISABEL</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -29242,33 +29226,29 @@
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S314" t="inlineStr"/>
       <c r="T314" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr"/>
       <c r="V314" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29300,12 +29280,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>C004204018</t>
+          <t>C004094472</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>C004204018 - DIAZ TANAKA ROXANA CECILIA</t>
+          <t>C004094472 - QUINTANILLA HERRERA BRANDOT ANTHONY</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -29336,12 +29316,12 @@
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -29394,12 +29374,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C004094472</t>
+          <t>C004204018</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>C004094472 - QUINTANILLA HERRERA BRANDOT ANTHONY</t>
+          <t>C004204018 - DIAZ TANAKA ROXANA CECILIA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -29430,12 +29410,12 @@
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -29478,7 +29458,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -29488,17 +29468,17 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>C004184900</t>
+          <t>C001740791</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>C004184900 - TORRES GONGORA CALISTO</t>
+          <t>C001740791 - ANYAIPOMA MONTES LEANDRA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I317" s="2" t="n">
@@ -29511,7 +29491,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -29522,19 +29502,35 @@
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
-      <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="inlineStr"/>
-      <c r="R317" t="inlineStr"/>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
       <c r="S317" t="inlineStr"/>
       <c r="T317" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29566,12 +29562,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>C004188961</t>
+          <t>C001692252</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>C004188961 - VELARDE ASCONA DELIA ISABEL</t>
+          <t>C001692252 - SALAZAR HUARACHI CRHISTIAN JEFFERSON</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -29602,29 +29598,33 @@
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S318" t="inlineStr"/>
       <c r="T318" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29656,12 +29656,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>C001757239</t>
+          <t>C001762483</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>C001757239 - ESPINOZA SUICA PAMELA ALESSANDRA</t>
+          <t>C001762483 - CCAIHUARI ROJAS OLGA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -29692,17 +29692,17 @@
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S319" t="inlineStr"/>
@@ -29750,12 +29750,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C001762483</t>
+          <t>C001757239</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>C001762483 - CCAIHUARI ROJAS OLGA</t>
+          <t>C001757239 - ESPINOZA SUICA PAMELA ALESSANDRA</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -29786,17 +29786,17 @@
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S320" t="inlineStr"/>
@@ -29844,12 +29844,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C001692252</t>
+          <t>C001744346</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>C001692252 - SALAZAR HUARACHI CRHISTIAN JEFFERSON</t>
+          <t>C001744346 - SANCHEZ CABALLERO SANDRA JULIANA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -30122,12 +30122,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>C001392016</t>
+          <t>C001436333</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>C001392016 - VELIZ PACHECO NELLY PIEDAD</t>
+          <t>C001436333 - RAMOS SALINAS MARIA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -30216,17 +30216,17 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>C001398220</t>
+          <t>C001408383</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>C001398220 - TERRAZAS DURAND CARMEN EFILIA</t>
+          <t>C001408383 - SACSA ARRIETA LIDIA RENE</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I325" s="2" t="n">
@@ -30239,7 +30239,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -30250,19 +30250,35 @@
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="inlineStr"/>
       <c r="O325" t="inlineStr"/>
-      <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="inlineStr"/>
-      <c r="R325" t="inlineStr"/>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>Mejor experiencia con la app</t>
+        </is>
+      </c>
       <c r="S325" t="inlineStr"/>
       <c r="T325" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U325" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V325" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -30294,12 +30310,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>C001408383</t>
+          <t>C001392016</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>C001408383 - SACSA ARRIETA LIDIA RENE</t>
+          <t>C001392016 - VELIZ PACHECO NELLY PIEDAD</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -30335,12 +30351,12 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S326" t="inlineStr"/>
@@ -30351,12 +30367,12 @@
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30378,7 +30394,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -30388,17 +30404,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>C001436333</t>
+          <t>C001398220</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>C001436333 - RAMOS SALINAS MARIA</t>
+          <t>C001398220 - TERRAZAS DURAND CARMEN EFILIA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I327" s="2" t="n">
@@ -30411,7 +30427,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -30422,35 +30438,19 @@
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr"/>
       <c r="T327" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr"/>
       <c r="V327" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
